--- a/business/estimate-template.xlsx
+++ b/business/estimate-template.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">発行者メール</t>
   </si>
   <si>
-    <t xml:space="preserve">eyu.eyu0806@gmail.com</t>
+    <t xml:space="preserve">yue.sadamatsu@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">基本範囲</t>
